--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEBRASKA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEBRASKA_2020.xlsx
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C46">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C64">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C97">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C116">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C150">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C154">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C161">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C251">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C395">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C408">
